--- a/experimental/attention/kv_cache_turbo_quant/task_submission/3.1 性能自验证报告.xlsx
+++ b/experimental/attention/kv_cache_turbo_quant/task_submission/3.1 性能自验证报告.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="1 性能数据" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="2 复跑波动" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="3 截图" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1 性能数据" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2 复跑波动" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3 口径说明" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -74,7 +74,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -89,7 +89,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -164,61 +163,6 @@
     </indexedColors>
   </colors>
 </styleSheet>
-</file>
-
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>1</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="8572500" cy="6562725"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="1" name="Image 1" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>40</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="8572500" cy="1323975"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="2" name="Image 2" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-</wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -532,7 +476,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>硬件：Atlas 800T A2（910B3）×1　CANN：9.1.0　torch 2.9.0 / torch_npu 2.9.0.post6　计时程序：算子仓 examples 编译出的 test_aclnn_kv_cache_turbo_quant（aclnn 两段式调用）</t>
+          <t>硬件：Atlas 800T A2（910B3）×1　CANN：9.1.0　torch 2.7.1 / torch_npu 2.7.1.post4　Python：3.11.4　计时程序：算子仓 examples 编译出的 test_aclnn_kv_cache_turbo_quant（aclnn 两段式调用）</t>
         </is>
       </c>
     </row>
@@ -546,7 +490,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>基线：任务书 §3.5 给定 PyTorch eager baseline；门槛：加速比 ≥ 10×。</t>
+          <t>基线：任务书 §3.5 给定 PyTorch eager baseline（只读）；门槛：加速比 ≥ 10×。</t>
         </is>
       </c>
     </row>
@@ -603,11 +547,11 @@
         <v>149.2</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>50.4</v>
+        <v>64</v>
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>29.60×</t>
+          <t>23.31×</t>
         </is>
       </c>
       <c r="G9" s="4" t="inlineStr">
@@ -632,11 +576,11 @@
         <v>155.3</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>74</v>
+        <v>85.2</v>
       </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t>20.98×</t>
+          <t>18.23×</t>
         </is>
       </c>
       <c r="G10" s="4" t="inlineStr">
@@ -661,11 +605,11 @@
         <v>385.5</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>332.2</v>
+        <v>277.1</v>
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>11.61×</t>
+          <t>13.91×</t>
         </is>
       </c>
       <c r="G11" s="4" t="inlineStr">
@@ -690,11 +634,11 @@
         <v>360.8</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>273.1</v>
+        <v>226.3</v>
       </c>
       <c r="F12" s="4" t="inlineStr">
         <is>
-          <t>13.21×</t>
+          <t>15.94×</t>
         </is>
       </c>
       <c r="G12" s="4" t="inlineStr">
@@ -719,11 +663,11 @@
         <v>528.7</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>379.8</v>
+        <v>308.6</v>
       </c>
       <c r="F13" s="4" t="inlineStr">
         <is>
-          <t>13.92×</t>
+          <t>17.13×</t>
         </is>
       </c>
       <c r="G13" s="4" t="inlineStr">
@@ -735,7 +679,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>5/5 case 达成 ≥10×；最小加速比为 gqa_prefill_t2048：11.61×。</t>
+          <t>5/5 case 达成 ≥10×；最小加速比为 gqa_prefill_t2048：13.91×，余量 39.1%。</t>
         </is>
       </c>
     </row>
@@ -756,7 +700,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G12"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -813,19 +757,19 @@
         </is>
       </c>
       <c r="B3" s="4" t="n">
-        <v>50.4</v>
+        <v>69</v>
       </c>
       <c r="C3" s="4" t="n">
-        <v>64.59999999999999</v>
+        <v>85.8</v>
       </c>
       <c r="D3" s="4" t="n">
-        <v>330.5</v>
+        <v>281.9</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>277</v>
+        <v>221.9</v>
       </c>
       <c r="F3" s="4" t="n">
-        <v>383.2</v>
+        <v>314</v>
       </c>
     </row>
     <row r="4">
@@ -835,147 +779,117 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>48.4</v>
+        <v>66.5</v>
       </c>
       <c r="C4" s="4" t="n">
-        <v>67.8</v>
+        <v>83.90000000000001</v>
       </c>
       <c r="D4" s="4" t="n">
-        <v>339</v>
+        <v>275</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>274.5</v>
+        <v>221.5</v>
       </c>
       <c r="F4" s="4" t="n">
-        <v>382.1</v>
+        <v>313.3</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>截图轮（随附截图）</t>
+          <t>本轮（本报告数据）</t>
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>51.5</v>
+        <v>64</v>
       </c>
       <c r="C5" s="4" t="n">
-        <v>74.90000000000001</v>
+        <v>85.2</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>335.6</v>
+        <v>277.1</v>
       </c>
       <c r="E5" s="4" t="n">
-        <v>279.2</v>
+        <v>226.3</v>
       </c>
       <c r="F5" s="4" t="n">
-        <v>379.9</v>
+        <v>308.6</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="inlineStr">
-        <is>
-          <t>本轮（本报告数据）</t>
-        </is>
-      </c>
-      <c r="B6" s="4" t="n">
-        <v>50.4</v>
-      </c>
-      <c r="C6" s="4" t="n">
-        <v>74</v>
-      </c>
-      <c r="D6" s="4" t="n">
-        <v>332.2</v>
-      </c>
-      <c r="E6" s="4" t="n">
-        <v>273.1</v>
-      </c>
-      <c r="F6" s="4" t="n">
-        <v>379.8</v>
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>极差（相对均值）</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>7.5%</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>2.2%</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>2.5%</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>2.2%</t>
+        </is>
+      </c>
+      <c r="F6" s="5" t="inlineStr">
+        <is>
+          <t>1.7%</t>
+        </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>极差（相对均值）</t>
+          <t>最差轮加速比（baseline ÷ 最差中位数）</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>6.2%</t>
+          <t>21.62×</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>14.6%</t>
+          <t>18.10×</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>2.5%</t>
+          <t>13.68×</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
-          <t>2.2%</t>
+          <t>15.94×</t>
         </is>
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>0.9%</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="5" t="inlineStr">
-        <is>
-          <t>最差轮加速比（baseline ÷ 最差中位数）</t>
-        </is>
-      </c>
-      <c r="B8" s="5" t="inlineStr">
-        <is>
-          <t>28.96×</t>
-        </is>
-      </c>
-      <c r="C8" s="5" t="inlineStr">
-        <is>
-          <t>20.73×</t>
-        </is>
-      </c>
-      <c r="D8" s="5" t="inlineStr">
-        <is>
-          <t>11.37×</t>
-        </is>
-      </c>
-      <c r="E8" s="5" t="inlineStr">
-        <is>
-          <t>12.92×</t>
-        </is>
-      </c>
-      <c r="F8" s="5" t="inlineStr">
-        <is>
-          <t>13.80×</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>波动原因：计时环内含 workspace 分配（t2048 档约 50MB）与 kernel launch，设备内存分配器状态与调度会使轮间中位数产生抖动；上表即为同条件复跑的实测范围。各轮最差中位数仍满足 ≥10×（最低 11.37×，gqa_prefill_t2048）。</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>随附性能截图（本报告「3 截图」页）拍摄于上表「截图轮」，与本报告采用的「本轮」为同机同条件相邻轮，差异落在上表极差范围内。</t>
+          <t>16.84×</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>波动原因：计时环内含 workspace 分配与 kernel launch，设备内存分配器状态与调度会使轮间中位数产生抖动；上表即为同条件复跑的实测范围。各轮最差中位数仍满足 ≥10×（最低 13.68×）。本轮的 workspace 规模为 t2048 档 33.88MB（LibApi 16MB + 2×8192KB 行缓冲 + 65KB），落在运行时 aclrtMalloc 内存池快路径（实测 ~2µs）；行缓冲按「阶段互斥」把 residual 别名到 unit 缓冲、projection 别名到 rotated 缓冲，故比未裁剪版（50.92MB，malloc ~53µs）快。详见 alias/README.md 与 alias/wsbytes_cost.log。</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A10:G10"/>
-    <mergeCell ref="A12:G12"/>
+  <mergeCells count="1">
+    <mergeCell ref="A9:G9"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -987,25 +901,43 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A40"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="6" t="inlineStr">
-        <is>
-          <t>截图 1：5 个 case 一键自测汇总（含各 case 中位数与判定）</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="6" t="inlineStr">
-        <is>
-          <t>截图 2：性能原始样本（gqa_prefill_t2048, bits=3，warmup 3 + repeat 10 全序列）</t>
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>性能口径说明与补充数据</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>① 本报告采用「示例驱动」口径（与交付日志 3.2 一致）：计时环内含 workspace 申请。该口径的绝对值受宿主侧 aclrtMalloc 开销影响，跨环境比较需注意。</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>② 补充口径（记为 Q6）：workspace 在计时环外申请、跨迭代复用，其余不变。同一内核、同一 case（gqa_prefill_t2048, bits=3）在本环境实测 0.2664ms → 14.47×（数值由原始日志 kctq_deliv_q6.log 解析，不手填；口径差异见 docs/evidence/repro/2026-09-30_kctq_bitexact_reverse/perf_ab.md）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>③ 截图：本轮重新截取（8 张），内容逐行取自本轮原始日志，与 `2.2/3.2` 一致；见 `2.1 精度自验证报告.xlsx` 的「3 截图」页。</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A6:G6"/>
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A4:G4"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
--- a/experimental/attention/kv_cache_turbo_quant/task_submission/3.1 性能自验证报告.xlsx
+++ b/experimental/attention/kv_cache_turbo_quant/task_submission/3.1 性能自验证报告.xlsx
@@ -8,8 +8,9 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1 性能数据" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2 复跑波动" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3 口径说明" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2 官方协议 3 轮" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3 示例驱动口径" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="4 口径说明" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -454,7 +455,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G14"/>
+  <dimension ref="A1:G16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -476,140 +477,89 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>硬件：Atlas 800T A2（910B3）×1　CANN：9.1.0　torch 2.7.1 / torch_npu 2.7.1.post4　Python：3.11.4　计时程序：算子仓 examples 编译出的 test_aclnn_kv_cache_turbo_quant（aclnn 两段式调用）</t>
+          <t>硬件：Atlas 800T A2（910B3）×1　CANN：9.1.0　torch 2.7.1 / torch_npu 2.7.1.post4　Python：3.11.4</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>计时口径：warmup 3 次 + 计次 10 次，取中位数（latency_ms_median）；计时环内含 workspace 分配（aclrtMalloc）、kernel launch 与 stream 同步；不含输入/输出数据在 host 与 device 间搬运。</t>
+          <t>【主口径】官方 Q6 协议：warmup 20 次 + 100 次设备计时 + 3 轮取中位数；不计输入准备、数据搬运、首次编译及 workspace 申请。计时程序：算子仓 .runtime/op_test/kctq_run（workspace 在计时环外申请、跨迭代复用）。</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
+          <t>【附表】示例驱动口径（更严）：warmup 3 次 + 计次 10 次，取中位数；计时环内含 workspace 分配（aclrtMalloc）+ kernel launch + stream 同步。它比官方口径多计一次 malloc，作为保守下界并列上报；见「3 示例驱动口径」页。</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
           <t>基线：任务书 §3.5 给定 PyTorch eager baseline（只读）；门槛：加速比 ≥ 10×。</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="3" t="inlineStr">
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
         <is>
           <t>case</t>
         </is>
       </c>
-      <c r="B8" s="3" t="inlineStr">
+      <c r="B10" s="3" t="inlineStr">
         <is>
           <t>mse_bits</t>
         </is>
       </c>
-      <c r="C8" s="3" t="inlineStr">
+      <c r="C10" s="3" t="inlineStr">
         <is>
           <t>baseline (µs)</t>
         </is>
       </c>
-      <c r="D8" s="3" t="inlineStr">
+      <c r="D10" s="3" t="inlineStr">
         <is>
           <t>10× 目标 (µs)</t>
         </is>
       </c>
-      <c r="E8" s="3" t="inlineStr">
-        <is>
-          <t>实测中位数 (µs)</t>
-        </is>
-      </c>
-      <c r="F8" s="3" t="inlineStr">
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>3 轮中位数 (µs)</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
         <is>
           <t>加速比</t>
         </is>
       </c>
-      <c r="G8" s="3" t="inlineStr">
+      <c r="G10" s="3" t="inlineStr">
         <is>
           <t>判定</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="4" t="inlineStr">
-        <is>
-          <t>gqa_decode_b1</t>
-        </is>
-      </c>
-      <c r="B9" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="C9" s="4" t="n">
-        <v>1491.676</v>
-      </c>
-      <c r="D9" s="4" t="n">
-        <v>149.2</v>
-      </c>
-      <c r="E9" s="4" t="n">
-        <v>64</v>
-      </c>
-      <c r="F9" s="4" t="inlineStr">
-        <is>
-          <t>23.31×</t>
-        </is>
-      </c>
-      <c r="G9" s="4" t="inlineStr">
-        <is>
-          <t>通过</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="4" t="inlineStr">
-        <is>
-          <t>gqa_decode_b64</t>
-        </is>
-      </c>
-      <c r="B10" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="C10" s="4" t="n">
-        <v>1552.784</v>
-      </c>
-      <c r="D10" s="4" t="n">
-        <v>155.3</v>
-      </c>
-      <c r="E10" s="4" t="n">
-        <v>85.2</v>
-      </c>
-      <c r="F10" s="4" t="inlineStr">
-        <is>
-          <t>18.23×</t>
-        </is>
-      </c>
-      <c r="G10" s="4" t="inlineStr">
-        <is>
-          <t>通过</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>gqa_prefill_t2048</t>
+          <t>gqa_decode_b1</t>
         </is>
       </c>
       <c r="B11" s="4" t="n">
         <v>3</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>3855.422</v>
+        <v>1491.676</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>385.5</v>
+        <v>149.2</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>277.1</v>
+        <v>43.1</v>
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>13.91×</t>
+          <t>34.61×</t>
         </is>
       </c>
       <c r="G11" s="4" t="inlineStr">
@@ -621,24 +571,24 @@
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>gqa_mse2_t2048</t>
+          <t>gqa_decode_b64</t>
         </is>
       </c>
       <c r="B12" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>3607.963</v>
+        <v>1552.784</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>360.8</v>
+        <v>155.3</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>226.3</v>
+        <v>73.7</v>
       </c>
       <c r="F12" s="4" t="inlineStr">
         <is>
-          <t>15.94×</t>
+          <t>21.07×</t>
         </is>
       </c>
       <c r="G12" s="4" t="inlineStr">
@@ -650,51 +600,269 @@
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
+          <t>gqa_prefill_t2048</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="C13" s="4" t="n">
+        <v>3855.422</v>
+      </c>
+      <c r="D13" s="4" t="n">
+        <v>385.5</v>
+      </c>
+      <c r="E13" s="4" t="n">
+        <v>263.7</v>
+      </c>
+      <c r="F13" s="4" t="inlineStr">
+        <is>
+          <t>14.62×</t>
+        </is>
+      </c>
+      <c r="G13" s="4" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>gqa_mse2_t2048</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="C14" s="4" t="n">
+        <v>3607.963</v>
+      </c>
+      <c r="D14" s="4" t="n">
+        <v>360.8</v>
+      </c>
+      <c r="E14" s="4" t="n">
+        <v>210</v>
+      </c>
+      <c r="F14" s="4" t="inlineStr">
+        <is>
+          <t>17.18×</t>
+        </is>
+      </c>
+      <c r="G14" s="4" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
           <t>gqa_mse4_t2048</t>
         </is>
       </c>
-      <c r="B13" s="4" t="n">
+      <c r="B15" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="C13" s="4" t="n">
+      <c r="C15" s="4" t="n">
         <v>5286.502</v>
       </c>
-      <c r="D13" s="4" t="n">
+      <c r="D15" s="4" t="n">
         <v>528.7</v>
       </c>
-      <c r="E13" s="4" t="n">
-        <v>308.6</v>
-      </c>
-      <c r="F13" s="4" t="inlineStr">
-        <is>
-          <t>17.13×</t>
-        </is>
-      </c>
-      <c r="G13" s="4" t="inlineStr">
+      <c r="E15" s="4" t="n">
+        <v>300.9</v>
+      </c>
+      <c r="F15" s="4" t="inlineStr">
+        <is>
+          <t>17.57×</t>
+        </is>
+      </c>
+      <c r="G15" s="4" t="inlineStr">
         <is>
           <t>通过</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>5/5 case 达成 ≥10×；最小加速比为 gqa_prefill_t2048：13.91×，余量 39.1%。</t>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>5/5 case 达成 ≥10×；最小加速比为 gqa_prefill_t2048：14.62×，余量 46.2%。</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="4">
-    <mergeCell ref="A14:G14"/>
+  <mergeCells count="5">
+    <mergeCell ref="A8:G8"/>
     <mergeCell ref="A6:G6"/>
+    <mergeCell ref="A4:G4"/>
     <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A4:G4"/>
+    <mergeCell ref="A16:G16"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>官方 Q6 协议：warmup=20 / repeat=100 / 3 轮明细（单位 µs）</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>轮次</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>gqa_decode_b1</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>gqa_decode_b64</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>gqa_prefill_t2048</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>gqa_mse2_t2048</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>gqa_mse4_t2048</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>官方协议轮次 1</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="n">
+        <v>42</v>
+      </c>
+      <c r="C3" s="4" t="n">
+        <v>73.7</v>
+      </c>
+      <c r="D3" s="4" t="n">
+        <v>263.5</v>
+      </c>
+      <c r="E3" s="4" t="n">
+        <v>210</v>
+      </c>
+      <c r="F3" s="4" t="n">
+        <v>299.6</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>官方协议轮次 2</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="n">
+        <v>47.7</v>
+      </c>
+      <c r="C4" s="4" t="n">
+        <v>72.7</v>
+      </c>
+      <c r="D4" s="4" t="n">
+        <v>266.1</v>
+      </c>
+      <c r="E4" s="4" t="n">
+        <v>211.9</v>
+      </c>
+      <c r="F4" s="4" t="n">
+        <v>300.9</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>官方协议轮次 3</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="n">
+        <v>43.1</v>
+      </c>
+      <c r="C5" s="4" t="n">
+        <v>74.8</v>
+      </c>
+      <c r="D5" s="4" t="n">
+        <v>263.7</v>
+      </c>
+      <c r="E5" s="4" t="n">
+        <v>207.7</v>
+      </c>
+      <c r="F5" s="4" t="n">
+        <v>322.6</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>3 轮中位数（判定用）</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="n">
+        <v>43.1</v>
+      </c>
+      <c r="C6" s="4" t="n">
+        <v>73.7</v>
+      </c>
+      <c r="D6" s="4" t="n">
+        <v>263.7</v>
+      </c>
+      <c r="E6" s="4" t="n">
+        <v>210</v>
+      </c>
+      <c r="F6" s="4" t="n">
+        <v>300.9</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>依据：官方 2026-09-30 答复（discussions/14 Q6）。workspace 申请在计时环外，故本表不受宿主侧 aclrtMalloc 开销影响。</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A7:G7"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -714,7 +882,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>同条件复跑（同一提交、同一机器、同一命令）</t>
+          <t>示例驱动口径（更严：含 workspace 申请）—— 同条件复跑（同一提交、同一机器、同一命令）</t>
         </is>
       </c>
     </row>
@@ -757,19 +925,19 @@
         </is>
       </c>
       <c r="B3" s="4" t="n">
-        <v>69</v>
+        <v>60.3</v>
       </c>
       <c r="C3" s="4" t="n">
-        <v>85.8</v>
+        <v>81.3</v>
       </c>
       <c r="D3" s="4" t="n">
-        <v>281.9</v>
+        <v>272.8</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>221.9</v>
+        <v>219.8</v>
       </c>
       <c r="F3" s="4" t="n">
-        <v>314</v>
+        <v>312.1</v>
       </c>
     </row>
     <row r="4">
@@ -779,19 +947,19 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>66.5</v>
+        <v>69.7</v>
       </c>
       <c r="C4" s="4" t="n">
-        <v>83.90000000000001</v>
+        <v>81</v>
       </c>
       <c r="D4" s="4" t="n">
-        <v>275</v>
+        <v>271</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>221.5</v>
+        <v>220.2</v>
       </c>
       <c r="F4" s="4" t="n">
-        <v>313.3</v>
+        <v>307</v>
       </c>
     </row>
     <row r="5">
@@ -801,19 +969,19 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>64</v>
+        <v>62.7</v>
       </c>
       <c r="C5" s="4" t="n">
-        <v>85.2</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>277.1</v>
+        <v>274.8</v>
       </c>
       <c r="E5" s="4" t="n">
-        <v>226.3</v>
+        <v>224</v>
       </c>
       <c r="F5" s="4" t="n">
-        <v>308.6</v>
+        <v>343</v>
       </c>
     </row>
     <row r="6">
@@ -824,27 +992,27 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>7.5%</t>
+          <t>14.6%</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>2.2%</t>
+          <t>0.9%</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>2.5%</t>
+          <t>1.4%</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
-          <t>2.2%</t>
+          <t>1.9%</t>
         </is>
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>1.7%</t>
+          <t>11.2%</t>
         </is>
       </c>
     </row>
@@ -856,34 +1024,34 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>21.62×</t>
+          <t>21.40×</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>18.10×</t>
+          <t>19.10×</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>13.68×</t>
+          <t>14.03×</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
-          <t>15.94×</t>
+          <t>16.11×</t>
         </is>
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>16.84×</t>
+          <t>15.41×</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>波动原因：计时环内含 workspace 分配与 kernel launch，设备内存分配器状态与调度会使轮间中位数产生抖动；上表即为同条件复跑的实测范围。各轮最差中位数仍满足 ≥10×（最低 13.68×）。本轮的 workspace 规模为 t2048 档 33.88MB（LibApi 16MB + 2×8192KB 行缓冲 + 65KB），落在运行时 aclrtMalloc 内存池快路径（实测 ~2µs）；行缓冲按「阶段互斥」把 residual 别名到 unit 缓冲、projection 别名到 rotated 缓冲，故比未裁剪版（50.92MB，malloc ~53µs）快。详见 alias/README.md 与 alias/wsbytes_cost.log。</t>
+          <t>波动原因：计时环内含 workspace 分配与 kernel launch，设备内存分配器状态与调度会使轮间中位数产生抖动；上表即为同条件复跑的实测范围。各轮最差中位数仍满足 ≥10×（最低 14.03×）。本轮的 workspace 规模为 t2048 档 33.88MB（LibApi 16MB + 2×8192KB 行缓冲 + 65KB），落在运行时 aclrtMalloc 内存池快路径（实测 ~2µs）；行缓冲按「阶段互斥」把 residual 别名到 unit 缓冲、projection 别名到 rotated 缓冲，故比未裁剪版（50.92MB，malloc ~53µs）快。详见 alias/README.md 与 alias/wsbytes_cost.log。</t>
         </is>
       </c>
     </row>
@@ -895,7 +1063,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -914,21 +1082,21 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>① 本报告采用「示例驱动」口径（与交付日志 3.2 一致）：计时环内含 workspace 申请。该口径的绝对值受宿主侧 aclrtMalloc 开销影响，跨环境比较需注意。</t>
+          <t>① 【主口径】官方 Q6 协议（与 3.2 日志主段一致）：warmup 20 次 + 100 次设备计时 + 3 轮取中位数；不计输入准备、数据搬运、首次编译及 workspace 申请。依据 = 官方 2026-09-30 答复（discussions/14 Q6）。</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>② 补充口径（记为 Q6）：workspace 在计时环外申请、跨迭代复用，其余不变。同一内核、同一 case（gqa_prefill_t2048, bits=3）在本环境实测 0.2664ms → 14.47×（数值由原始日志 kctq_deliv_q6.log 解析，不手填；口径差异见 docs/evidence/repro/2026-09-30_kctq_bitexact_reverse/perf_ab.md）。</t>
+          <t>② 【附表】示例驱动口径（更严）：warmup 3 次 + 计次 10 次；计时环内含 workspace 申请。该口径的绝对值受宿主侧 aclrtMalloc 开销影响，跨环境比较需注意；本算子 t2048 档 workspace 33.88MB（≤35MB 快路径 ~2µs），未裁剪版 50.92MB 会掉到 ~53µs 慢路径（见 alias/README.md 与 alias/wsbytes_cost.log）。</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>③ 截图：本轮重新截取（8 张），内容逐行取自本轮原始日志，与 `2.2/3.2` 一致；见 `2.1 精度自验证报告.xlsx` 的「3 截图」页。</t>
+          <t>④ 截图：本轮重新截取（8 张），内容逐行取自本轮原始日志，与 `2.2/3.2` 一致；见 `2.1 精度自验证报告.xlsx` 的「3 截图」页。</t>
         </is>
       </c>
     </row>
